--- a/AF/test_cases.xlsx
+++ b/AF/test_cases.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>case_name</t>
   </si>
@@ -101,6 +101,96 @@
   </si>
   <si>
     <t>Test_AttentionToFFN_readLine_8die_ID002</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID003</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID004</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID005</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID006</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID007</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID008</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID009</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID010</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID011</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID012</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID013</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID014</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID015</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID016</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID017</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID018</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID019</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID020</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID021</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID022</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID023</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID024</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID025</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID026</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID027</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID028</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID029</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID030</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID031</t>
+  </si>
+  <si>
+    <t>Test_AttentionToFFN_readLine_8die_ID032</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1335,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -1506,6 +1596,1956 @@
       </c>
       <c r="U4">
         <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4096</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>4</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>7168</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>8</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>7168</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>128</v>
+      </c>
+      <c r="D8">
+        <v>4096</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>12</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>512</v>
+      </c>
+      <c r="D9">
+        <v>8192</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>8</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>7168</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>256</v>
+      </c>
+      <c r="D11">
+        <v>7168</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
+      </c>
+      <c r="N11">
+        <v>32</v>
+      </c>
+      <c r="O11">
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <v>4</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>2048</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>7</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>32</v>
+      </c>
+      <c r="D13">
+        <v>4096</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>4</v>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>4</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>64</v>
+      </c>
+      <c r="D14">
+        <v>7168</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <v>8</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>4</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>8192</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>4096</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>7168</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>7</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>12</v>
+      </c>
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>6</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>7168</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>4</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18">
+        <v>12</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+      <c r="P18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1024</v>
+      </c>
+      <c r="D19">
+        <v>4096</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <v>8</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+      <c r="P19">
+        <v>4</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>2048</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>6</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>64</v>
+      </c>
+      <c r="D21">
+        <v>7168</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>8</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>4</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>32</v>
+      </c>
+      <c r="D22">
+        <v>7168</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="N22">
+        <v>8</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <v>4</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>128</v>
+      </c>
+      <c r="D23">
+        <v>7168</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>8</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <v>4</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>32</v>
+      </c>
+      <c r="D24">
+        <v>4096</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <v>4</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>7168</v>
+      </c>
+      <c r="E25">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>6</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>12</v>
+      </c>
+      <c r="O25">
+        <v>4</v>
+      </c>
+      <c r="P25">
+        <v>3</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>3</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>4096</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>4</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <v>7168</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="N27">
+        <v>8</v>
+      </c>
+      <c r="O27">
+        <v>4</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>4096</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>6</v>
+      </c>
+      <c r="N28">
+        <v>8</v>
+      </c>
+      <c r="O28">
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>256</v>
+      </c>
+      <c r="D29">
+        <v>8192</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+      <c r="M29">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <v>8</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
+        <v>4</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>32</v>
+      </c>
+      <c r="D30">
+        <v>4096</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>4</v>
+      </c>
+      <c r="M30">
+        <v>4</v>
+      </c>
+      <c r="N30">
+        <v>8</v>
+      </c>
+      <c r="O30">
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <v>4</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>7168</v>
+      </c>
+      <c r="E31">
+        <v>32</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>4</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>64</v>
+      </c>
+      <c r="O31">
+        <v>16</v>
+      </c>
+      <c r="P31">
+        <v>4</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>32</v>
+      </c>
+      <c r="D32">
+        <v>7168</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>5</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>12</v>
+      </c>
+      <c r="O32">
+        <v>4</v>
+      </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>2</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>512</v>
+      </c>
+      <c r="D33">
+        <v>4096</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33">
+        <v>8</v>
+      </c>
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <v>4</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>2048</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <v>5</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
+      </c>
+      <c r="O34">
+        <v>2</v>
+      </c>
+      <c r="P34">
+        <v>2</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
